--- a/data/DAL.MI.xlsx
+++ b/data/DAL.MI.xlsx
@@ -62796,7 +62796,7 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
         <v>0</v>
@@ -62819,7 +62819,7 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
         <v>0</v>
@@ -62842,7 +62842,7 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
         <v>0</v>
@@ -62860,6 +62860,29 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G2717" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2718">
+      <c r="A2718" s="1" t="n">
+        <v>46275.2916666667</v>
+      </c>
+      <c r="B2718" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2718" t="n">
+        <v>5.69000005722046</v>
+      </c>
+      <c r="D2718" t="n">
+        <v>5.69000005722046</v>
+      </c>
+      <c r="E2718" t="n">
+        <v>5.69000005722046</v>
+      </c>
+      <c r="F2718" t="n">
+        <v>5.69000005722046</v>
+      </c>
+      <c r="G2718" t="s">
         <v>7</v>
       </c>
     </row>
